--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136339033</v>
       </c>
       <c r="B3" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
